--- a/ig/DM-37/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="131">
   <si>
     <t>Property</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,6 +243,24 @@
   </si>
   <si>
     <t>Avocat participant aux processus de soins sans consentement (eSSS)</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Assistant de service social (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Psychologue (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Psychothérapeute (Expérimentation MAIA)</t>
   </si>
   <si>
     <t>307</t>
@@ -871,7 +889,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1011,119 +1029,119 @@
         <v>98</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>46</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>50</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>111</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>113</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>115</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
@@ -1160,18 +1178,42 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B37" t="s" s="2">
-        <v>124</v>
+      <c r="B40" t="s" s="2">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
